--- a/output/sliding_window_results_window_5.xlsx
+++ b/output/sliding_window_results_window_5.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>30.48</v>
+        <v>38.5</v>
       </c>
       <c r="C2" t="n">
-        <v>29.24296621998221</v>
+        <v>38.55406767761049</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.237033780017793</v>
+        <v>0.05406767761049025</v>
       </c>
       <c r="E2" t="n">
-        <v>1.530252572905109</v>
+        <v>0.002923313762191909</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>30.95</v>
+        <v>40.1</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55377877806397</v>
+        <v>42.84887040319342</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3962212219360275</v>
+        <v>2.748870403193422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1569912567124787</v>
+        <v>7.556288493552766</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C4" t="n">
-        <v>31.21742119573918</v>
+        <v>42.7697575804067</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1625788042608214</v>
+        <v>1.269757580406704</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02643186759487847</v>
+        <v>1.612284313000288</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C5" t="n">
-        <v>31.81625205844014</v>
+        <v>48.39334397092941</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4637479415598591</v>
+        <v>4.693343970929405</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2150621533010065</v>
+        <v>22.02747762945939</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C6" t="n">
-        <v>32.58715208287603</v>
+        <v>54.14703259034588</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5128479171239704</v>
+        <v>6.047032590345879</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2630129860983948</v>
+        <v>36.56660314870518</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>34.47538792156094</v>
+        <v>60.55183903519452</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07538792156093876</v>
+        <v>7.551839035194519</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005683338717278255</v>
+        <v>57.03027281348768</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C8" t="n">
-        <v>34.98256761695012</v>
+        <v>63.96449248232587</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.317432383049876</v>
+        <v>7.864492482325872</v>
       </c>
       <c r="E8" t="n">
-        <v>1.735628083908476</v>
+        <v>61.85024200456016</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>37.79219309375701</v>
+        <v>62.73794573683015</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7078069062429933</v>
+        <v>2.737945736830149</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5009906165252774</v>
+        <v>7.496346857826386</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.41926745598487</v>
+        <v>68.60492227365663</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6807325440151288</v>
+        <v>4.704922273656628</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4633967964813093</v>
+        <v>22.13629360115025</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>40.90666638459123</v>
+        <v>73.30825919890779</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5933336154087669</v>
+        <v>2.708259198907797</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3520447791740386</v>
+        <v>7.334667888468702</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>44.44668612245557</v>
+        <v>84.60044936465383</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7466861224555643</v>
+        <v>3.700449364653821</v>
       </c>
       <c r="E12" t="n">
-        <v>0.557540165467726</v>
+        <v>13.69332550036687</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>46.23432342027743</v>
+        <v>86.7072423649557</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.865676579722575</v>
+        <v>-2.392757635044291</v>
       </c>
       <c r="E13" t="n">
-        <v>3.480749100125324</v>
+        <v>5.725289100062746</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C14" t="n">
-        <v>52.39382341206358</v>
+        <v>86.47024500226922</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6061765879364245</v>
+        <v>-8.529754997730777</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3674500557622458</v>
+        <v>72.75672032131317</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C15" t="n">
-        <v>55.81897352419305</v>
+        <v>98.44900936938345</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2810264758069536</v>
+        <v>-0.3509906306165504</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07897588010447629</v>
+        <v>0.1231944227806038</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C16" t="n">
-        <v>59.09910516576657</v>
+        <v>99.58552491326364</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9008948342334335</v>
+        <v>-3.714475086736357</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8116115023484857</v>
+        <v>13.79732516998507</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C17" t="n">
-        <v>61.76071237768966</v>
+        <v>107.3270667767578</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.139287622310334</v>
+        <v>0.3270667767577606</v>
       </c>
       <c r="E17" t="n">
-        <v>4.576551530970203</v>
+        <v>0.1069726764587108</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C18" t="n">
-        <v>69.80623041816359</v>
+        <v>118.865597166198</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7937695818364006</v>
+        <v>10.165597166198</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6300701490487343</v>
+        <v>103.3393657454128</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C19" t="n">
-        <v>79.15232200994275</v>
+        <v>120.1649420691556</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.747677990057255</v>
+        <v>7.46494206915564</v>
       </c>
       <c r="E19" t="n">
-        <v>3.054378356930568</v>
+        <v>55.72536009584969</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C20" t="n">
-        <v>89.25040235288506</v>
+        <v>129.1026995288111</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1504023528850666</v>
+        <v>11.90269952881108</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02262086775336412</v>
+        <v>141.6742560731596</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C21" t="n">
-        <v>93.11253234712596</v>
+        <v>126.8340859874721</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.887467652874037</v>
+        <v>3.734085987472099</v>
       </c>
       <c r="E21" t="n">
-        <v>3.562534140645825</v>
+        <v>13.94339816183548</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-15.32123604149108</v>
+        <v>62.68739349232129</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>22.3919762005752</v>
+        <v>644.4986073311976</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1.11959881002876</v>
+        <v>32.22493036655988</v>
       </c>
     </row>
   </sheetData>
